--- a/movies.xlsx
+++ b/movies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/syd/Desktop/Quickfox Internship/RTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63049F3-F5F7-BE4F-8D59-DD148AB4A521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CA392E-6012-2B48-A545-82D3608AA27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="760" windowWidth="18200" windowHeight="8500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,21 +20,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Movies</t>
   </si>
   <si>
-    <t>Beast</t>
-  </si>
-  <si>
     <t>The Drama</t>
   </si>
   <si>
     <t>A Great Awakening</t>
   </si>
   <si>
+    <t>Godfather</t>
+  </si>
+  <si>
+    <t>Heads Or Tails</t>
+  </si>
+  <si>
     <t>Titanic</t>
+  </si>
+  <si>
+    <t>this is a test movie nothing exists with this name 998908</t>
   </si>
 </sst>
 </file>
@@ -52,10 +58,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -66,7 +71,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -78,10 +90,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -387,35 +400,45 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/movies.xlsx
+++ b/movies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/syd/Desktop/Quickfox Internship/RTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CA392E-6012-2B48-A545-82D3608AA27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1722C374-F987-3145-BF7B-16E30E610481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="760" windowWidth="18200" windowHeight="8500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,27 +20,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Movies</t>
-  </si>
-  <si>
-    <t>The Drama</t>
-  </si>
-  <si>
-    <t>A Great Awakening</t>
-  </si>
-  <si>
-    <t>Godfather</t>
-  </si>
-  <si>
-    <t>Heads Or Tails</t>
   </si>
   <si>
     <t>Titanic</t>
   </si>
   <si>
     <t>this is a test movie nothing exists with this name 998908</t>
+  </si>
+  <si>
+    <t>Breaking Bad</t>
   </si>
 </sst>
 </file>
@@ -400,7 +391,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44.5" bestFit="1" customWidth="1"/>
@@ -411,34 +402,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
+    <row r="2" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
